--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="Questa_cartella_di_lavoro" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\DOC - Manuela Arigoni\SW PERSONALIZZATI\SW FERIE CLIENTI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuela.arigoni\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C5E49F-8AB6-45F1-A187-E0DCDC476CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{624D88D3-0513-4C2B-906B-12C24BAE0661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>EMAIL</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>arigoni.manuela@gmail.com</t>
+  </si>
+  <si>
+    <t>Ghidelli Patrizia</t>
+  </si>
+  <si>
+    <t>ufficio.amministrazioneò@wingaming.it</t>
+  </si>
+  <si>
+    <t>WinAmm2026</t>
   </si>
 </sst>
 </file>
@@ -233,12 +242,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -555,7 +566,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56295C2E-C6A6-445F-99D3-BA76E299DEF4}">
   <sheetPr codeName="Foglio1"/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -728,6 +739,20 @@
         <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -745,6 +770,7 @@
     <hyperlink ref="B12" r:id="rId9" xr:uid="{7C9ECE65-2AAC-4A18-9316-CD5B131DAB66}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{CB0ED145-0174-42AE-B2F7-0393391640A1}"/>
     <hyperlink ref="B10" r:id="rId11" xr:uid="{D7086F26-0731-4FFF-812B-B9C2337FBD3B}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{B0BC000B-03F8-4ACB-B83C-1E05FEB56B99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/elenco_tecnici.xlsx
+++ b/elenco_tecnici.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manuela.arigoni\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{624D88D3-0513-4C2B-906B-12C24BAE0661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AC07D0-8CA2-4B1C-8A03-3B230C1C33B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14745" yWindow="4305" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TECNICI" sheetId="3" r:id="rId1"/>
@@ -164,10 +164,10 @@
     <t>Ghidelli Patrizia</t>
   </si>
   <si>
-    <t>ufficio.amministrazioneò@wingaming.it</t>
-  </si>
-  <si>
     <t>WinAmm2026</t>
+  </si>
+  <si>
+    <t>ufficio.amministrazione@wingaming.it</t>
   </si>
 </sst>
 </file>
@@ -242,14 +242,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -743,16 +741,16 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
     </row>
